--- a/testData/TC_Copy_Quote.xlsx
+++ b/testData/TC_Copy_Quote.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation_Project\E2E_Automation\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netapp-my.sharepoint.com/personal/sunilr2_netapp_com/Documents/Desktop/Playwright Python/E2E_Automation/testData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F16471BE-40D5-471C-B595-18980636BD4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7D74A73F-B829-4A32-9C22-66E55DE688DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2FD946A-31BD-40FA-B9AD-6029E604E352}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="21600" windowHeight="13749" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t>User Name</t>
   </si>
@@ -36,15 +36,9 @@
     <t>Quote Name</t>
   </si>
   <si>
-    <t>Quote 344256 for Apple Inc. - T</t>
-  </si>
-  <si>
     <t>Navigate To URL</t>
   </si>
   <si>
-    <t>https://netapp2--uat.sandbox.lightning.force.com/lightning/r/Opportunity/006ce00000DyHsxAAF/view</t>
-  </si>
-  <si>
     <t>Quote Number</t>
   </si>
   <si>
@@ -118,6 +112,18 @@
   </si>
   <si>
     <t>PURCHASE ORDER</t>
+  </si>
+  <si>
+    <t>GTC</t>
+  </si>
+  <si>
+    <t>DR Override Justification</t>
+  </si>
+  <si>
+    <t>https://netapp2--uat.sandbox.lightning.force.com/lightning/r/Opportunity/006cW00000GFZgzQAH/view</t>
+  </si>
+  <si>
+    <t>Quote 710669 for Apple Inc.</t>
   </si>
 </sst>
 </file>
@@ -203,7 +209,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -221,6 +227,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -508,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="24.84375" bestFit="1" customWidth="1"/>
@@ -521,162 +531,173 @@
     <col min="8" max="8" width="22.23046875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.07421875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.3046875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.15234375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.61328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.3828125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.53515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.23046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.15234375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.61328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.3828125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
+      <c r="C2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
       <c r="K2" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="8"/>
+      <c r="L2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="10"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>22</v>
+      <c r="O3" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="43.75" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" ht="43.75" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2">
-        <v>344256</v>
+        <v>710669</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="L4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="E1:N1"/>
+    <mergeCell ref="E1:O1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{47EE4E77-2460-4481-AA44-A3339C5905D5}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{B6B5A508-9463-470C-9009-0617B23CBB4A}"/>
-    <hyperlink ref="M4" r:id="rId3" xr:uid="{A8B304BD-B6B8-4C14-A647-C22A11905C9C}"/>
+    <hyperlink ref="N4" r:id="rId2" xr:uid="{A8B304BD-B6B8-4C14-A647-C22A11905C9C}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{89B7FBDC-F438-4754-941B-F084ACE30777}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
